--- a/outputs/108-24.xlsx
+++ b/outputs/108-24.xlsx
@@ -941,16 +941,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1168,20 +1172,20 @@
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="38"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="n">
+      <c r="C1" s="2" t="n">
         <v>-14863.3912</v>
       </c>
-      <c r="D1" s="0" t="n">
+      <c r="D1" s="2" t="n">
         <v>-177880.6536</v>
       </c>
     </row>
@@ -1189,13 +1193,13 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="2" t="n">
         <v>347.826</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="2" t="n">
         <v>7239.808</v>
       </c>
     </row>
@@ -1203,13 +1207,13 @@
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="2" t="n">
         <v>-173.92</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="2" t="n">
         <v>-2347.9132</v>
       </c>
     </row>
@@ -1217,13 +1221,13 @@
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>790.8528</v>
       </c>
     </row>
@@ -1231,13 +1235,13 @@
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="2" t="n">
         <v>13196.7492</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="2" t="n">
         <v>160572.986</v>
       </c>
     </row>
@@ -1245,13 +1249,13 @@
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="2" t="n">
         <v>44.8792</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="2" t="n">
         <v>881.3692</v>
       </c>
     </row>
@@ -1259,13 +1263,13 @@
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>812.2328</v>
       </c>
     </row>
@@ -1273,13 +1277,13 @@
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="0" t="n">
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
         <v>53.36</v>
       </c>
     </row>
@@ -1287,13 +1291,13 @@
       <c r="A9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1301,13 +1305,13 @@
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="2" t="n">
         <v>456</v>
       </c>
     </row>
@@ -1315,13 +1319,13 @@
       <c r="A11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="0" t="n">
+      <c r="C11" s="2" t="n">
         <v>-11147.84</v>
       </c>
-      <c r="D11" s="0" t="n">
+      <c r="D11" s="2" t="n">
         <v>-168681.7984</v>
       </c>
     </row>
@@ -1329,13 +1333,13 @@
       <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="2" t="n">
         <v>347.826</v>
       </c>
-      <c r="D12" s="0" t="n">
+      <c r="D12" s="2" t="n">
         <v>4258.054</v>
       </c>
     </row>
@@ -1343,13 +1347,13 @@
       <c r="A13" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="2" t="n">
         <v>-189.96</v>
       </c>
-      <c r="D13" s="0" t="n">
+      <c r="D13" s="2" t="n">
         <v>-2885.76</v>
       </c>
     </row>
@@ -1357,13 +1361,13 @@
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="0" t="n">
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="n">
         <v>1746.6228</v>
       </c>
     </row>
@@ -1371,13 +1375,13 @@
       <c r="A15" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="2" t="n">
         <v>10110.3824</v>
       </c>
-      <c r="D15" s="0" t="n">
+      <c r="D15" s="2" t="n">
         <v>151448.7644</v>
       </c>
     </row>
@@ -1385,13 +1389,13 @@
       <c r="A16" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="2" t="n">
         <v>67.9704</v>
       </c>
-      <c r="D16" s="0" t="n">
+      <c r="D16" s="2" t="n">
         <v>1112.3976</v>
       </c>
     </row>
@@ -1399,13 +1403,13 @@
       <c r="A17" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="2" t="n">
         <v>5.196</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="2" t="n">
         <v>937.7116</v>
       </c>
     </row>
@@ -1413,13 +1417,13 @@
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="0" t="n">
+      <c r="C18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="n">
         <v>26.68</v>
       </c>
     </row>
@@ -1427,13 +1431,13 @@
       <c r="A19" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="0" t="n">
+      <c r="C19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1441,13 +1445,13 @@
       <c r="A20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C20" s="0" t="n">
+      <c r="C20" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D20" s="0" t="n">
+      <c r="D20" s="2" t="n">
         <v>156.348</v>
       </c>
     </row>
@@ -1455,13 +1459,13 @@
       <c r="A21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="0" t="s">
+      <c r="B21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C21" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="0" t="n">
+      <c r="C21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="2" t="n">
         <v>-29572.1808</v>
       </c>
     </row>
@@ -1469,13 +1473,13 @@
       <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="0" t="s">
+      <c r="B22" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="0" t="n">
+      <c r="C22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="2" t="n">
         <v>1137.3912</v>
       </c>
     </row>
@@ -1483,13 +1487,13 @@
       <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="0" t="s">
+      <c r="B23" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C23" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="0" t="n">
+      <c r="C23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="2" t="n">
         <v>-584.32</v>
       </c>
     </row>
@@ -1497,13 +1501,13 @@
       <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="0" t="s">
+      <c r="B24" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="0" t="n">
+      <c r="C24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1511,13 +1515,13 @@
       <c r="A25" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="0" t="s">
+      <c r="B25" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="0" t="n">
+      <c r="C25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="n">
         <v>26283.2008</v>
       </c>
     </row>
@@ -1525,13 +1529,13 @@
       <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="0" t="s">
+      <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C26" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="0" t="n">
+      <c r="C26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="2" t="n">
         <v>104.5212</v>
       </c>
     </row>
@@ -1539,13 +1543,13 @@
       <c r="A27" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="0" t="s">
+      <c r="B27" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="0" t="n">
+      <c r="C27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="2" t="n">
         <v>5.428</v>
       </c>
     </row>
@@ -1553,13 +1557,13 @@
       <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="0" t="s">
+      <c r="B28" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="0" t="n">
+      <c r="C28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1567,13 +1571,13 @@
       <c r="A29" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="0" t="s">
+      <c r="B29" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C29" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="0" t="n">
+      <c r="C29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1581,13 +1585,13 @@
       <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="0" t="s">
+      <c r="B30" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C30" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="0" t="n">
+      <c r="C30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="n">
         <v>76</v>
       </c>
     </row>
@@ -1595,13 +1599,13 @@
       <c r="A31" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="0" t="s">
+      <c r="B31" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C31" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="0" t="n">
+      <c r="C31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="n">
         <v>-123474.7892</v>
       </c>
     </row>
@@ -1609,13 +1613,13 @@
       <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="0" t="s">
+      <c r="B32" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C32" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="0" t="n">
+      <c r="C32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="2" t="n">
         <v>3494.8716</v>
       </c>
     </row>
@@ -1623,13 +1627,13 @@
       <c r="A33" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="0" t="s">
+      <c r="B33" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="0" t="n">
+      <c r="C33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="2" t="n">
         <v>-1965.16</v>
       </c>
     </row>
@@ -1637,13 +1641,13 @@
       <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="0" t="s">
+      <c r="B34" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C34" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="0" t="n">
+      <c r="C34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="2" t="n">
         <v>1200.0992</v>
       </c>
     </row>
@@ -1651,13 +1655,13 @@
       <c r="A35" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="0" t="s">
+      <c r="B35" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C35" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" s="0" t="n">
+      <c r="C35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="2" t="n">
         <v>112415.2444</v>
       </c>
     </row>
@@ -1665,13 +1669,13 @@
       <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="0" t="s">
+      <c r="B36" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C36" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="0" t="n">
+      <c r="C36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="n">
         <v>521.4108</v>
       </c>
     </row>
@@ -1679,13 +1683,13 @@
       <c r="A37" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="0" t="s">
+      <c r="B37" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C37" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="0" t="n">
+      <c r="C37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="n">
         <v>678.8348</v>
       </c>
     </row>
@@ -1693,13 +1697,13 @@
       <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="0" t="s">
+      <c r="B38" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="0" t="n">
+      <c r="C38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="2" t="n">
         <v>53.36</v>
       </c>
     </row>
@@ -1707,13 +1711,13 @@
       <c r="A39" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="0" t="s">
+      <c r="B39" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C39" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" s="0" t="n">
+      <c r="C39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1721,13 +1725,13 @@
       <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="0" t="s">
+      <c r="B40" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C40" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="0" t="n">
+      <c r="C40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="2" t="n">
         <v>266</v>
       </c>
     </row>
@@ -1735,13 +1739,13 @@
       <c r="A41" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="0" t="s">
+      <c r="B41" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C41" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="0" t="n">
+      <c r="C41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1749,13 +1753,13 @@
       <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="0" t="s">
+      <c r="B42" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="0" t="n">
+      <c r="C42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1763,13 +1767,13 @@
       <c r="A43" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="0" t="s">
+      <c r="B43" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C43" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="0" t="n">
+      <c r="C43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1777,13 +1781,13 @@
       <c r="A44" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="0" t="s">
+      <c r="B44" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C44" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" s="0" t="n">
+      <c r="C44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1791,13 +1795,13 @@
       <c r="A45" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="0" t="s">
+      <c r="B45" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C45" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="0" t="n">
+      <c r="C45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1805,13 +1809,13 @@
       <c r="A46" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B46" s="0" t="s">
+      <c r="B46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="0" t="n">
+      <c r="C46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1819,13 +1823,13 @@
       <c r="A47" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="0" t="s">
+      <c r="B47" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C47" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="0" t="n">
+      <c r="C47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1833,13 +1837,13 @@
       <c r="A48" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B48" s="0" t="s">
+      <c r="B48" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C48" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="0" t="n">
+      <c r="C48" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1847,13 +1851,13 @@
       <c r="A49" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B49" s="0" t="s">
+      <c r="B49" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C49" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="0" t="n">
+      <c r="C49" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1861,13 +1865,13 @@
       <c r="A50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="0" t="s">
+      <c r="B50" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="0" t="n">
+      <c r="C50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1875,13 +1879,13 @@
       <c r="A51" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="0" t="s">
+      <c r="B51" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C51" s="0" t="n">
+      <c r="C51" s="2" t="n">
         <v>-21627.826</v>
       </c>
-      <c r="D51" s="0" t="n">
+      <c r="D51" s="2" t="n">
         <v>-592351.2648</v>
       </c>
     </row>
@@ -1889,13 +1893,13 @@
       <c r="A52" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B52" s="0" t="s">
+      <c r="B52" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C52" s="0" t="n">
+      <c r="C52" s="2" t="n">
         <v>695.652</v>
       </c>
-      <c r="D52" s="0" t="n">
+      <c r="D52" s="2" t="n">
         <v>19560.8448</v>
       </c>
     </row>
@@ -1903,13 +1907,13 @@
       <c r="A53" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="0" t="s">
+      <c r="B53" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C53" s="0" t="n">
+      <c r="C53" s="2" t="n">
         <v>-226.08</v>
       </c>
-      <c r="D53" s="0" t="n">
+      <c r="D53" s="2" t="n">
         <v>-6626</v>
       </c>
     </row>
@@ -1917,13 +1921,13 @@
       <c r="A54" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B54" s="0" t="s">
+      <c r="B54" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C54" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="0" t="n">
+      <c r="C54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="2" t="n">
         <v>5519.0104</v>
       </c>
     </row>
@@ -1931,13 +1935,13 @@
       <c r="A55" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="B55" s="0" t="s">
+      <c r="B55" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C55" s="0" t="n">
+      <c r="C55" s="2" t="n">
         <v>18812.0348</v>
       </c>
-      <c r="D55" s="0" t="n">
+      <c r="D55" s="2" t="n">
         <v>521520.2512</v>
       </c>
     </row>
@@ -1945,13 +1949,13 @@
       <c r="A56" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="0" t="s">
+      <c r="B56" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C56" s="0" t="n">
+      <c r="C56" s="2" t="n">
         <v>47.6812</v>
       </c>
-      <c r="D56" s="0" t="n">
+      <c r="D56" s="2" t="n">
         <v>1752.6528</v>
       </c>
     </row>
@@ -1959,13 +1963,13 @@
       <c r="A57" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="0" t="s">
+      <c r="B57" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C57" s="0" t="n">
+      <c r="C57" s="2" t="n">
         <v>20</v>
       </c>
-      <c r="D57" s="0" t="n">
+      <c r="D57" s="2" t="n">
         <v>1051.6676</v>
       </c>
     </row>
@@ -1973,13 +1977,13 @@
       <c r="A58" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="0" t="s">
+      <c r="B58" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C58" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="0" t="n">
+      <c r="C58" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="2" t="n">
         <v>26.68</v>
       </c>
     </row>
@@ -1987,13 +1991,13 @@
       <c r="A59" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B59" s="0" t="s">
+      <c r="B59" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C59" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="0" t="n">
+      <c r="C59" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2001,13 +2005,13 @@
       <c r="A60" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="0" t="s">
+      <c r="B60" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C60" s="0" t="n">
+      <c r="C60" s="2" t="n">
         <v>38</v>
       </c>
-      <c r="D60" s="0" t="n">
+      <c r="D60" s="2" t="n">
         <v>688.348</v>
       </c>
     </row>
@@ -2015,13 +2019,13 @@
       <c r="A61" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B61" s="0" t="s">
+      <c r="B61" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C61" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="0" t="n">
+      <c r="C61" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="2" t="n">
         <v>-1126.956</v>
       </c>
     </row>
@@ -2029,13 +2033,13 @@
       <c r="A62" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B62" s="0" t="s">
+      <c r="B62" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C62" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="0" t="n">
+      <c r="C62" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2043,13 +2047,13 @@
       <c r="A63" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B63" s="0" t="s">
+      <c r="B63" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C63" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" s="0" t="n">
+      <c r="C63" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2057,13 +2061,13 @@
       <c r="A64" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="B64" s="0" t="s">
+      <c r="B64" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C64" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="0" t="n">
+      <c r="C64" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2071,13 +2075,13 @@
       <c r="A65" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B65" s="0" t="s">
+      <c r="B65" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C65" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="0" t="n">
+      <c r="C65" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2085,13 +2089,13 @@
       <c r="A66" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B66" s="0" t="s">
+      <c r="B66" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C66" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" s="0" t="n">
+      <c r="C66" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2099,13 +2103,13 @@
       <c r="A67" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="B67" s="0" t="s">
+      <c r="B67" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C67" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="0" t="n">
+      <c r="C67" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2113,13 +2117,13 @@
       <c r="A68" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="0" t="s">
+      <c r="B68" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C68" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="0" t="n">
+      <c r="C68" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2127,13 +2131,13 @@
       <c r="A69" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="0" t="s">
+      <c r="B69" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C69" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="0" t="n">
+      <c r="C69" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2141,13 +2145,13 @@
       <c r="A70" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B70" s="0" t="s">
+      <c r="B70" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C70" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="0" t="n">
+      <c r="C70" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2155,13 +2159,13 @@
       <c r="A71" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C71" s="0" t="n">
+      <c r="C71" s="2" t="n">
         <v>-15652.1736</v>
       </c>
-      <c r="D71" s="0" t="n">
+      <c r="D71" s="2" t="n">
         <v>-228806.4752</v>
       </c>
     </row>
@@ -2169,13 +2173,13 @@
       <c r="A72" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="0" t="s">
+      <c r="B72" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C72" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" s="0" t="n">
+      <c r="C72" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2183,13 +2187,13 @@
       <c r="A73" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="B73" s="0" t="s">
+      <c r="B73" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C73" s="0" t="n">
+      <c r="C73" s="2" t="n">
         <v>-295.64</v>
       </c>
-      <c r="D73" s="0" t="n">
+      <c r="D73" s="2" t="n">
         <v>-4993.12</v>
       </c>
     </row>
@@ -2197,13 +2201,13 @@
       <c r="A74" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="B74" s="0" t="s">
+      <c r="B74" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C74" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" s="0" t="n">
+      <c r="C74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="2" t="n">
         <v>7065.7108</v>
       </c>
     </row>
@@ -2211,13 +2215,13 @@
       <c r="A75" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B75" s="0" t="s">
+      <c r="B75" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C75" s="0" t="n">
+      <c r="C75" s="2" t="n">
         <v>14963.9388</v>
       </c>
-      <c r="D75" s="0" t="n">
+      <c r="D75" s="2" t="n">
         <v>222005.55</v>
       </c>
     </row>
@@ -2225,13 +2229,13 @@
       <c r="A76" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B76" s="0" t="s">
+      <c r="B76" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C76" s="0" t="n">
+      <c r="C76" s="2" t="n">
         <v>66.7432</v>
       </c>
-      <c r="D76" s="0" t="n">
+      <c r="D76" s="2" t="n">
         <v>4109.876</v>
       </c>
     </row>
@@ -2239,13 +2243,13 @@
       <c r="A77" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C77" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" s="0" t="n">
+      <c r="C77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="2" t="n">
         <v>1105.6268</v>
       </c>
     </row>
@@ -2253,13 +2257,13 @@
       <c r="A78" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B78" s="0" t="s">
+      <c r="B78" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C78" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" s="0" t="n">
+      <c r="C78" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="2" t="n">
         <v>26.68</v>
       </c>
     </row>
@@ -2267,13 +2271,13 @@
       <c r="A79" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B79" s="0" t="s">
+      <c r="B79" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C79" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" s="0" t="n">
+      <c r="C79" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2281,13 +2285,13 @@
       <c r="A80" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C80" s="0" t="n">
+      <c r="C80" s="2" t="n">
         <v>-149.6</v>
       </c>
-      <c r="D80" s="0" t="n">
+      <c r="D80" s="2" t="n">
         <v>-12837.42</v>
       </c>
     </row>
@@ -2295,13 +2299,13 @@
       <c r="A81" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B81" s="0" t="s">
+      <c r="B81" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C81" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" s="0" t="n">
+      <c r="C81" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2309,13 +2313,13 @@
       <c r="A82" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B82" s="0" t="s">
+      <c r="B82" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C82" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" s="0" t="n">
+      <c r="C82" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2323,13 +2327,13 @@
       <c r="A83" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C83" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" s="0" t="n">
+      <c r="C83" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2337,13 +2341,13 @@
       <c r="A84" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B84" s="0" t="s">
+      <c r="B84" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C84" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" s="0" t="n">
+      <c r="C84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2351,13 +2355,13 @@
       <c r="A85" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B85" s="0" t="s">
+      <c r="B85" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C85" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" s="0" t="n">
+      <c r="C85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2365,13 +2369,13 @@
       <c r="A86" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B86" s="0" t="s">
+      <c r="B86" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C86" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" s="0" t="n">
+      <c r="C86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D86" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2379,13 +2383,13 @@
       <c r="A87" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B87" s="0" t="s">
+      <c r="B87" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C87" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" s="0" t="n">
+      <c r="C87" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D87" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2393,13 +2397,13 @@
       <c r="A88" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B88" s="0" t="s">
+      <c r="B88" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C88" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" s="0" t="n">
+      <c r="C88" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D88" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2407,13 +2411,13 @@
       <c r="A89" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B89" s="0" t="s">
+      <c r="B89" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C89" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" s="0" t="n">
+      <c r="C89" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2421,13 +2425,13 @@
       <c r="A90" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B90" s="0" t="s">
+      <c r="B90" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C90" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" s="0" t="n">
+      <c r="C90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D90" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2435,13 +2439,13 @@
       <c r="A91" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B91" s="0" t="s">
+      <c r="B91" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="C91" s="0" t="n">
+      <c r="C91" s="2" t="n">
         <v>-9787.2116</v>
       </c>
-      <c r="D91" s="0" t="n">
+      <c r="D91" s="2" t="n">
         <v>-158107.13</v>
       </c>
     </row>
@@ -2449,13 +2453,13 @@
       <c r="A92" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B92" s="0" t="s">
+      <c r="B92" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C92" s="0" t="n">
+      <c r="C92" s="2" t="n">
         <v>9787.2116</v>
       </c>
-      <c r="D92" s="0" t="n">
+      <c r="D92" s="2" t="n">
         <v>158063.5836</v>
       </c>
     </row>
@@ -2463,13 +2467,13 @@
       <c r="A93" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B93" s="0" t="s">
+      <c r="B93" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="C93" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" s="0" t="n">
+      <c r="C93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2477,13 +2481,13 @@
       <c r="A94" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B94" s="0" t="s">
+      <c r="B94" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C94" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" s="0" t="n">
+      <c r="C94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D94" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2491,13 +2495,13 @@
       <c r="A95" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B95" s="0" t="s">
+      <c r="B95" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C95" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" s="0" t="n">
+      <c r="C95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2505,13 +2509,13 @@
       <c r="A96" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B96" s="0" t="s">
+      <c r="B96" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C96" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" s="0" t="n">
+      <c r="C96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D96" s="2" t="n">
         <v>112521.74</v>
       </c>
     </row>
@@ -2519,13 +2523,13 @@
       <c r="A97" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B97" s="0" t="s">
+      <c r="B97" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C97" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" s="0" t="n">
+      <c r="C97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D97" s="2" t="n">
         <v>509.038</v>
       </c>
     </row>
@@ -2533,13 +2537,13 @@
       <c r="A98" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B98" s="0" t="s">
+      <c r="B98" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C98" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" s="0" t="n">
+      <c r="C98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D98" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2547,13 +2551,13 @@
       <c r="A99" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B99" s="0" t="s">
+      <c r="B99" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C99" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" s="0" t="n">
+      <c r="C99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D99" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2561,13 +2565,13 @@
       <c r="A100" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B100" s="0" t="s">
+      <c r="B100" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C100" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" s="0" t="n">
+      <c r="C100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2575,13 +2579,13 @@
       <c r="A101" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B101" s="0" t="s">
+      <c r="B101" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C101" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="0" t="n">
+      <c r="C101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="2" t="n">
         <v>400</v>
       </c>
     </row>
@@ -2589,13 +2593,13 @@
       <c r="A102" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B102" s="0" t="s">
+      <c r="B102" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C102" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" s="0" t="n">
+      <c r="C102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="2" t="n">
         <v>-48852.172</v>
       </c>
     </row>
@@ -2603,13 +2607,13 @@
       <c r="A103" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B103" s="0" t="s">
+      <c r="B103" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C103" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" s="0" t="n">
+      <c r="C103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2617,13 +2621,13 @@
       <c r="A104" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B104" s="0" t="s">
+      <c r="B104" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C104" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" s="0" t="n">
+      <c r="C104" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="2" t="n">
         <v>-957.4</v>
       </c>
     </row>
@@ -2631,13 +2635,13 @@
       <c r="A105" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B105" s="0" t="s">
+      <c r="B105" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="C105" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" s="0" t="n">
+      <c r="C105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2645,13 +2649,13 @@
       <c r="A106" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B106" s="0" t="s">
+      <c r="B106" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C106" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" s="0" t="n">
+      <c r="C106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D106" s="2" t="n">
         <v>47671.578</v>
       </c>
     </row>
@@ -2659,13 +2663,13 @@
       <c r="A107" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B107" s="0" t="s">
+      <c r="B107" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C107" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" s="0" t="n">
+      <c r="C107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="2" t="n">
         <v>178</v>
       </c>
     </row>
@@ -2673,13 +2677,13 @@
       <c r="A108" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B108" s="0" t="s">
+      <c r="B108" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C108" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" s="0" t="n">
+      <c r="C108" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2687,13 +2691,13 @@
       <c r="A109" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B109" s="0" t="s">
+      <c r="B109" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C109" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" s="0" t="n">
+      <c r="C109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="2" t="n">
         <v>133.4</v>
       </c>
     </row>
@@ -2701,13 +2705,13 @@
       <c r="A110" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B110" s="0" t="s">
+      <c r="B110" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C110" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" s="0" t="n">
+      <c r="C110" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2715,13 +2719,13 @@
       <c r="A111" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B111" s="0" t="s">
+      <c r="B111" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C111" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" s="0" t="n">
+      <c r="C111" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="2" t="n">
         <v>-1004.2</v>
       </c>
     </row>
@@ -2729,13 +2733,13 @@
       <c r="A112" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B112" s="0" t="s">
+      <c r="B112" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="C112" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" s="0" t="n">
+      <c r="C112" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="2" t="n">
         <v>-184650.838</v>
       </c>
     </row>
@@ -2743,13 +2747,13 @@
       <c r="A113" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B113" s="0" t="s">
+      <c r="B113" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C113" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" s="0" t="n">
+      <c r="C113" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="2" t="n">
         <v>181814.788</v>
       </c>
     </row>
@@ -2757,13 +2761,13 @@
       <c r="A114" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B114" s="0" t="s">
+      <c r="B114" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C114" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" s="0" t="n">
+      <c r="C114" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="2" t="n">
         <v>-6724.116</v>
       </c>
     </row>
@@ -2771,13 +2775,13 @@
       <c r="A115" s="1" t="s">
         <v>228</v>
       </c>
-      <c r="B115" s="0" t="s">
+      <c r="B115" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C115" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" s="0" t="n">
+      <c r="C115" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2785,13 +2789,13 @@
       <c r="A116" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="B116" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C116" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" s="0" t="n">
+      <c r="C116" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2799,13 +2803,13 @@
       <c r="A117" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B117" s="0" t="s">
+      <c r="B117" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C117" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" s="0" t="n">
+      <c r="C117" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2813,13 +2817,13 @@
       <c r="A118" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="B118" s="0" t="s">
+      <c r="B118" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="C118" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" s="0" t="n">
+      <c r="C118" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="2" t="n">
         <v>-1351685.478</v>
       </c>
     </row>
@@ -2827,13 +2831,13 @@
       <c r="A119" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B119" s="0" t="s">
+      <c r="B119" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C119" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" s="0" t="n">
+      <c r="C119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="2" t="n">
         <v>1354135.444</v>
       </c>
     </row>
@@ -2841,13 +2845,13 @@
       <c r="A120" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B120" s="0" t="s">
+      <c r="B120" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C120" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" s="0" t="n">
+      <c r="C120" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2855,13 +2859,13 @@
       <c r="A121" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B121" s="0" t="s">
+      <c r="B121" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="C121" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" s="0" t="n">
+      <c r="C121" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2869,13 +2873,13 @@
       <c r="A122" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B122" s="0" t="s">
+      <c r="B122" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="C122" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" s="0" t="n">
+      <c r="C122" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2883,13 +2887,13 @@
       <c r="A123" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B123" s="0" t="s">
+      <c r="B123" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C123" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" s="0" t="n">
+      <c r="C123" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="2" t="n">
         <v>-2526.318</v>
       </c>
     </row>
@@ -2897,13 +2901,13 @@
       <c r="A124" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B124" s="0" t="s">
+      <c r="B124" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="C124" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" s="0" t="n">
+      <c r="C124" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="2" t="n">
         <v>883.628</v>
       </c>
     </row>
@@ -2911,13 +2915,13 @@
       <c r="A125" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B125" s="0" t="s">
+      <c r="B125" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="C125" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" s="0" t="n">
+      <c r="C125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2925,13 +2929,13 @@
       <c r="A126" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B126" s="0" t="s">
+      <c r="B126" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C126" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" s="0" t="n">
+      <c r="C126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="2" t="n">
         <v>65.942</v>
       </c>
     </row>
@@ -2939,13 +2943,13 @@
       <c r="A127" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="B127" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="C127" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" s="0" t="n">
+      <c r="C127" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D127" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2953,13 +2957,13 @@
       <c r="A128" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B128" s="0" t="s">
+      <c r="B128" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="C128" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" s="0" t="n">
+      <c r="C128" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="2" t="n">
         <v>-86.99</v>
       </c>
     </row>
@@ -2967,13 +2971,13 @@
       <c r="A129" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B129" s="0" t="s">
+      <c r="B129" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="C129" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" s="0" t="n">
+      <c r="C129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D129" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2981,13 +2985,13 @@
       <c r="A130" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B130" s="0" t="s">
+      <c r="B130" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="C130" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" s="0" t="n">
+      <c r="C130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D130" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2995,13 +2999,13 @@
       <c r="A131" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B131" s="0" t="s">
+      <c r="B131" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="C131" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" s="0" t="n">
+      <c r="C131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3009,13 +3013,13 @@
       <c r="A132" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B132" s="0" t="s">
+      <c r="B132" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="C132" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" s="0" t="n">
+      <c r="C132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D132" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3023,13 +3027,13 @@
       <c r="A133" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B133" s="0" t="s">
+      <c r="B133" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C133" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" s="0" t="n">
+      <c r="C133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D133" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3037,13 +3041,13 @@
       <c r="A134" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B134" s="0" t="s">
+      <c r="B134" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="C134" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" s="0" t="n">
+      <c r="C134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="2" t="n">
         <v>-6085.218</v>
       </c>
     </row>
@@ -3051,13 +3055,13 @@
       <c r="A135" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B135" s="0" t="s">
+      <c r="B135" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="C135" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" s="0" t="n">
+      <c r="C135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D135" s="2" t="n">
         <v>5020.304</v>
       </c>
     </row>
@@ -3065,13 +3069,13 @@
       <c r="A136" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B136" s="0" t="s">
+      <c r="B136" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C136" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" s="0" t="n">
+      <c r="C136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D136" s="2" t="n">
         <v>-3182.608</v>
       </c>
     </row>
@@ -3079,13 +3083,13 @@
       <c r="A137" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B137" s="0" t="s">
+      <c r="B137" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C137" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" s="0" t="n">
+      <c r="C137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D137" s="2" t="n">
         <v>1535.218</v>
       </c>
     </row>
@@ -3093,13 +3097,13 @@
       <c r="A138" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B138" s="0" t="s">
+      <c r="B138" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="C138" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" s="0" t="n">
+      <c r="C138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D138" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3107,13 +3111,13 @@
       <c r="A139" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B139" s="0" t="s">
+      <c r="B139" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C139" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" s="0" t="n">
+      <c r="C139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D139" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3121,13 +3125,13 @@
       <c r="A140" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B140" s="0" t="s">
+      <c r="B140" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C140" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" s="0" t="n">
+      <c r="C140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D140" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3152,21 +3156,21 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="39.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="36.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="2" width="39.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1" s="0" t="n">
+      <c r="C1" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="n">
         <v>112521.74</v>
       </c>
     </row>
@@ -3174,13 +3178,13 @@
       <c r="A2" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="0" t="n">
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>509.038</v>
       </c>
     </row>
@@ -3188,13 +3192,13 @@
       <c r="A3" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3202,13 +3206,13 @@
       <c r="A4" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3216,13 +3220,13 @@
       <c r="A5" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3230,13 +3234,13 @@
       <c r="A6" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="0" t="n">
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>400</v>
       </c>
     </row>
@@ -3244,13 +3248,13 @@
       <c r="A7" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>47671.578</v>
       </c>
     </row>
@@ -3258,13 +3262,13 @@
       <c r="A8" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="0" t="n">
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
         <v>178</v>
       </c>
     </row>
@@ -3272,13 +3276,13 @@
       <c r="A9" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3286,13 +3290,13 @@
       <c r="A10" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="0" t="n">
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>133.4</v>
       </c>
     </row>
@@ -3300,13 +3304,13 @@
       <c r="A11" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3314,13 +3318,13 @@
       <c r="A12" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="0" t="n">
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="n">
         <v>-1004.2</v>
       </c>
     </row>
@@ -3328,13 +3332,13 @@
       <c r="A13" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="0" t="n">
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="n">
         <v>181814.788</v>
       </c>
     </row>
@@ -3342,13 +3346,13 @@
       <c r="A14" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="0" t="n">
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="n">
         <v>-6724.116</v>
       </c>
     </row>
@@ -3356,13 +3360,13 @@
       <c r="A15" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="0" t="n">
+      <c r="C15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3370,13 +3374,13 @@
       <c r="A16" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="0" t="n">
+      <c r="C16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3384,13 +3388,13 @@
       <c r="A17" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="0" t="n">
+      <c r="C17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>1354135.444</v>
       </c>
     </row>
@@ -3398,13 +3402,13 @@
       <c r="A18" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="0" t="n">
+      <c r="C18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3427,258 +3431,258 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="36.44"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C1" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D1" s="0" t="n">
+      <c r="C1" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="n">
         <v>112521.74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" s="0" t="n">
+      <c r="C2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>509.038</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" s="0" t="n">
+      <c r="C3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" s="0" t="n">
+      <c r="C4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="0" t="n">
+      <c r="C5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="0" t="n">
+      <c r="C6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="0" t="n">
+      <c r="C7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="n">
         <v>47671.578</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="0" t="n">
+      <c r="C8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="2" t="n">
         <v>178</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="C9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="0" t="n">
+      <c r="C9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="C10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="0" t="n">
+      <c r="C10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>133.4</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="0" t="n">
+      <c r="C11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="C12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="0" t="n">
+      <c r="C12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="n">
         <v>-1004.2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="0" t="n">
+      <c r="C13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="n">
         <v>181814.788</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="0" t="n">
+      <c r="C14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="2" t="n">
         <v>-6724.116</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="C15" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="0" t="n">
+      <c r="C15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="C16" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="0" t="n">
+      <c r="C16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="C17" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="0" t="n">
+      <c r="C17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="2" t="n">
         <v>1354135.444</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="C18" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="0" t="n">
+      <c r="C18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="2" t="n">
         <v>0</v>
       </c>
     </row>
